--- a/chemical_database.xlsx
+++ b/chemical_database.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="59">
   <si>
     <t>Searched Chemical Name</t>
   </si>
@@ -35,6 +35,9 @@
     <t>SDS Link</t>
   </si>
   <si>
+    <t>Storage Notes</t>
+  </si>
+  <si>
     <t>SDS Revision Date</t>
   </si>
   <si>
@@ -92,7 +95,7 @@
     <t>Pictogram Codes (for export)</t>
   </si>
   <si>
-    <t>SDS DOT Class (fix later)</t>
+    <t>Generated Classification (Class)</t>
   </si>
   <si>
     <t>PubChem CID Number</t>
@@ -144,7 +147,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Barium nitrate</t>
+      <t>N/A</t>
     </r>
     <r>
       <t xml:space="preserve">
@@ -248,6 +251,9 @@
   </si>
   <si>
     <t>https://www.fishersci.com/store/msds?partNumber=AC192555000&amp;productDescription=barium-nitrate-acs-reag-kg&amp;vendorId=VN00032119&amp;keyword=true&amp;countryCode=US&amp;language=en</t>
+  </si>
+  <si>
+    <t>Keep containers tightly closed in a dry, cool and well-ventilated place. Do not store near combustible materials. Incompatible Materials. Organic materials. Acids. Bases. Acid anhydrides. Metals. Reducing Agent. Strong reducing agents. Combustible material.</t>
   </si>
   <si>
     <t>24-Dec-2021</t>
@@ -280,7 +286,7 @@
   <si>
     <t xml:space="preserve">May intensify fire; oxidizer Toxic if swallowed 
 Causes serious eye irritation 
-Harmful if inhaled Company Fisher Scientific Company One Reagent Lane Fair Lawn, NJ 07410 Tel: (201) 796-7100 Acros Organics One Reagent Lane Fair Lawn, NJ 07410 Acute oral toxicity Category 3 Acute Inhalation Toxicity - Dusts and Mists Category 4 Serious Eye Damage/Eye Irritation Category 2 Oxidizing solids Category 2</t>
+Harmful if inhaled 0 Acute oral toxicity Category 3 Acute Inhalation Toxicity - Dusts and Mists Category 4 Serious Eye Damage/Eye Irritation Category 2 Oxidizing solids Category 2</t>
   </si>
   <si>
     <t xml:space="preserve">H272 (68.7%): May intensify fire; oxidizer [Danger Oxidizing liquids; Oxidizing solids]
@@ -302,16 +308,13 @@
 Health Hazard</t>
   </si>
   <si>
-    <t>temp</t>
-  </si>
-  <si>
-    <t>5.1</t>
+    <t>Inorganic salt</t>
   </si>
   <si>
     <t>EM Science</t>
   </si>
   <si>
-    <t>500 g</t>
+    <t>g</t>
   </si>
   <si>
     <t>6-144</t>
@@ -744,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ2"/>
+  <dimension ref="A1:AR2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -753,46 +756,46 @@
     <col min="4" max="4" width="24" style="1" customWidth="1"/>
     <col min="5" max="5" width="22" style="1" customWidth="1"/>
     <col min="6" max="6" width="90" style="1" customWidth="1"/>
-    <col min="7" max="7" width="100" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8" style="1" customWidth="1"/>
-    <col min="10" max="10" width="2" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19" style="1" customWidth="1"/>
-    <col min="13" max="13" width="23" style="1" customWidth="1"/>
-    <col min="14" max="14" width="2" style="1" customWidth="1"/>
-    <col min="15" max="15" width="21" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16" style="1" customWidth="1"/>
-    <col min="17" max="17" width="24" style="1" customWidth="1"/>
-    <col min="18" max="18" width="2" style="1" customWidth="1"/>
-    <col min="19" max="19" width="45" style="1" customWidth="1"/>
-    <col min="20" max="20" width="88" style="1" customWidth="1"/>
-    <col min="21" max="21" width="2" style="1" customWidth="1"/>
-    <col min="22" max="22" width="23" style="1" customWidth="1"/>
-    <col min="23" max="23" width="27" style="1" customWidth="1"/>
-    <col min="24" max="24" width="2" style="1" customWidth="1"/>
-    <col min="25" max="25" width="22" style="1" customWidth="1"/>
-    <col min="26" max="26" width="26" style="1" customWidth="1"/>
-    <col min="27" max="27" width="2" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17" style="1" customWidth="1"/>
-    <col min="29" max="29" width="21" style="1" customWidth="1"/>
-    <col min="30" max="30" width="2" style="1" customWidth="1"/>
-    <col min="31" max="31" width="100" style="1" customWidth="1"/>
-    <col min="32" max="32" width="100" style="2" customWidth="1"/>
-    <col min="33" max="33" width="45" style="1" customWidth="1"/>
-    <col min="34" max="34" width="30" style="1" customWidth="1"/>
-    <col min="35" max="35" width="27" style="1" customWidth="1"/>
-    <col min="36" max="36" width="2" style="1" customWidth="1"/>
-    <col min="37" max="37" width="20" style="1" customWidth="1"/>
-    <col min="38" max="38" width="12" style="1" customWidth="1"/>
-    <col min="39" max="39" width="10" style="1" customWidth="1"/>
-    <col min="40" max="40" width="7" style="1" customWidth="1"/>
-    <col min="41" max="41" width="10" style="1" customWidth="1"/>
-    <col min="42" max="42" width="9" style="1" customWidth="1"/>
-    <col min="43" max="43" width="15" style="1" customWidth="1"/>
+    <col min="7" max="8" width="100" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8" style="1" customWidth="1"/>
+    <col min="11" max="11" width="2" style="1" customWidth="1"/>
+    <col min="12" max="12" width="24" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19" style="1" customWidth="1"/>
+    <col min="14" max="14" width="23" style="1" customWidth="1"/>
+    <col min="15" max="15" width="2" style="1" customWidth="1"/>
+    <col min="16" max="16" width="21" style="1" customWidth="1"/>
+    <col min="17" max="17" width="16" style="1" customWidth="1"/>
+    <col min="18" max="18" width="24" style="1" customWidth="1"/>
+    <col min="19" max="19" width="2" style="1" customWidth="1"/>
+    <col min="20" max="20" width="45" style="1" customWidth="1"/>
+    <col min="21" max="21" width="88" style="1" customWidth="1"/>
+    <col min="22" max="22" width="2" style="1" customWidth="1"/>
+    <col min="23" max="23" width="23" style="1" customWidth="1"/>
+    <col min="24" max="24" width="27" style="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="1" customWidth="1"/>
+    <col min="26" max="26" width="22" style="1" customWidth="1"/>
+    <col min="27" max="27" width="26" style="1" customWidth="1"/>
+    <col min="28" max="28" width="2" style="1" customWidth="1"/>
+    <col min="29" max="29" width="17" style="1" customWidth="1"/>
+    <col min="30" max="30" width="21" style="1" customWidth="1"/>
+    <col min="31" max="31" width="2" style="1" customWidth="1"/>
+    <col min="32" max="32" width="100" style="1" customWidth="1"/>
+    <col min="33" max="33" width="100" style="2" customWidth="1"/>
+    <col min="34" max="34" width="45" style="1" customWidth="1"/>
+    <col min="35" max="35" width="30" style="1" customWidth="1"/>
+    <col min="36" max="36" width="34" style="1" customWidth="1"/>
+    <col min="37" max="37" width="2" style="1" customWidth="1"/>
+    <col min="38" max="38" width="20" style="1" customWidth="1"/>
+    <col min="39" max="39" width="12" style="1" customWidth="1"/>
+    <col min="40" max="40" width="10" style="1" customWidth="1"/>
+    <col min="41" max="41" width="7" style="1" customWidth="1"/>
+    <col min="42" max="42" width="10" style="1" customWidth="1"/>
+    <col min="43" max="43" width="9" style="1" customWidth="1"/>
+    <col min="44" max="44" width="15" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -820,76 +823,76 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>0</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="4" t="s">
+      <c r="N1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>1</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>12</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="S1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>14</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="U1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="V1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>16</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="W1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>18</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="Z1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>20</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="AC1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AE1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AG1" s="6" t="s">
         <v>24</v>
       </c>
       <c r="AH1" s="4" t="s">
@@ -898,11 +901,11 @@
       <c r="AI1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AJ1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK1" s="4" t="s">
+      <c r="AJ1" s="4" t="s">
         <v>27</v>
+      </c>
+      <c r="AK1" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="AL1" s="4" t="s">
         <v>28</v>
@@ -922,127 +925,130 @@
       <c r="AQ1" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="AR1" s="4" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" s="7">
         <v>90</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="7" t="s">
         <v>35</v>
       </c>
+      <c r="N2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="P2" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="7" t="s">
         <v>44</v>
       </c>
+      <c r="U2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="W2" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="7" t="s">
         <v>46</v>
       </c>
+      <c r="X2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y2" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="Z2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB2" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="AG2" s="7" t="s">
+      <c r="AD2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF2" s="7" t="s">
         <v>50</v>
       </c>
+      <c r="AG2" s="8" t="s">
+        <v>51</v>
+      </c>
       <c r="AH2" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="AJ2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK2" s="7">
+        <v>10</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL2" s="7">
         <v>24798</v>
-      </c>
-      <c r="AL2" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="AM2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="AN2" s="7" t="s">
-        <v>9</v>
+      <c r="AN2" s="7">
+        <v>500</v>
       </c>
       <c r="AO2" s="7" t="s">
         <v>55</v>
@@ -1052,6 +1058,9 @@
       </c>
       <c r="AQ2" s="7" t="s">
         <v>57</v>
+      </c>
+      <c r="AR2" s="7" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/chemical_database.xlsx
+++ b/chemical_database.xlsx
@@ -1,29 +1,388 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_043CF576C06DBA89714CD768DBDE48D32B30913F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Success Report" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Full Data" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Export" state="visible" r:id="rId6"/>
+    <sheet name="Full Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Success Report" sheetId="2" r:id="rId2"/>
+    <sheet name="Export" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="88">
+  <si>
+    <t>SEARCHED</t>
+  </si>
+  <si>
+    <t>SUMMARY</t>
+  </si>
+  <si>
+    <t>COMPARE</t>
+  </si>
+  <si>
+    <t>IMPORTED</t>
+  </si>
+  <si>
+    <t>PUBCHEM</t>
+  </si>
+  <si>
+    <t>SDS SHEET</t>
+  </si>
+  <si>
+    <t>HAZARDS</t>
+  </si>
+  <si>
+    <t>PICTOGRAMS</t>
+  </si>
+  <si>
+    <t>MISC 1</t>
+  </si>
+  <si>
+    <t>MISC 2</t>
+  </si>
+  <si>
+    <t>Barium nitrate</t>
+  </si>
+  <si>
+    <t>STATUS CODE:</t>
+  </si>
+  <si>
+    <t>✅✅ Extremely Confident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAME: </t>
+  </si>
+  <si>
+    <t>BARIUM NITRATE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May intensify fire; oxidizer 
+Toxic if swallowed 
+Causes serious eye irritation </t>
+  </si>
+  <si>
+    <t>Oxidizer
+Acute Toxic
+Irritant
+Health Hazard</t>
+  </si>
+  <si>
+    <t>CLASS:</t>
+  </si>
+  <si>
+    <t>Inorganic salt</t>
+  </si>
+  <si>
+    <t>RECEIVED DATE</t>
+  </si>
+  <si>
+    <t>No date</t>
+  </si>
+  <si>
+    <t>CONFIDENCE SCORE:</t>
+  </si>
+  <si>
+    <t>CAS NO.:</t>
+  </si>
+  <si>
+    <t>10022-31-8</t>
+  </si>
+  <si>
+    <t>SUPPLIER:</t>
+  </si>
+  <si>
+    <t>EM Science</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDS LINK: </t>
+  </si>
+  <si>
+    <t>Click for SDS.</t>
+  </si>
+  <si>
+    <t>CONF. SCORE INFO:</t>
+  </si>
+  <si>
+    <t>Molecular Formulas (normalized) do not match
+SDS: BAN2O6
+PubChem: BA(NO3)2
+Penalty: -10</t>
+  </si>
+  <si>
+    <t>SYNONYMS:</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Nitrobarite
+Nitric acid, barium salt
+Barium dinitrate
+Nitrate de baryum
+Nitrato barico</t>
+  </si>
+  <si>
+    <t>Barium dinitrate; Nitric acid
+barium salt.</t>
+  </si>
+  <si>
+    <t>QUANTITY:</t>
+  </si>
+  <si>
+    <t>STORAGE NOTES:</t>
+  </si>
+  <si>
+    <t>Keep containers tightly closed in a dry, cool and well-ventilated place. Do not store near combustible materials. Incompatible Materials. Organic materials. Acids. Bases. Acid anhydrides. Metals. Reducing Agent. Strong reducing agents. Combustible material.</t>
+  </si>
+  <si>
+    <t>FORMULA:</t>
+  </si>
+  <si>
+    <t>Ba(NO3)2</t>
+  </si>
+  <si>
+    <t>BaN2O6</t>
+  </si>
+  <si>
+    <t>H272 (68.7%): May intensify fire; oxidizer [Danger Oxidizing liquids; Oxidizing solids]
+H301 (12.2%): Toxic if swallowed [Danger Acute toxicity, oral]
+H302 (86.6%): Harmful if swallowed [Warning Acute toxicity, oral]
+H319 (24.8%): Causes serious eye irritation [Warning Serious eye damage/eye irritation]
+H332 (98.8%): Harmful if inhaled [Warning Acute toxicity, inhalation]
+H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H336: May cause drowsiness or dizziness [Warning Specific target organ toxicity, single exposure; Narcotic effects]
+H370: Causes damage to organs [Danger Specific target organ toxicity, single exposure]
+H371: May cause damage to organs [Warning Specific target organ toxicity, single exposure]
+H372: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
+H316: Causes mild skin irritation [Warning Skin corrosion/irritation]</t>
+  </si>
+  <si>
+    <t>OX
+AC
+IR
+CA</t>
+  </si>
+  <si>
+    <t>UNITS:</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>MW:</t>
+  </si>
+  <si>
+    <t>261.34</t>
+  </si>
+  <si>
+    <t>LOCATION:</t>
+  </si>
+  <si>
+    <t>6-144</t>
+  </si>
+  <si>
+    <t>ERRORS:</t>
+  </si>
+  <si>
+    <t>SIGNAL WORD:</t>
+  </si>
+  <si>
+    <t>Danger</t>
+  </si>
+  <si>
+    <t>CABINET:</t>
+  </si>
+  <si>
+    <t>A-1</t>
+  </si>
+  <si>
+    <t>1-napthol</t>
+  </si>
+  <si>
+    <t>1-NAPHTHOL</t>
+  </si>
+  <si>
+    <t>1-Naphthol</t>
+  </si>
+  <si>
+    <t>Causes skin irritation 
+Causes serious eye damage 
+May cause respiratory irritation 
+Harmful if swallowed or in contact with skin</t>
+  </si>
+  <si>
+    <t>Corrosive
+Irritant
+Acute Toxic
+Environmental Hazard
+Health Hazard</t>
+  </si>
+  <si>
+    <t>Organic compound</t>
+  </si>
+  <si>
+    <t>90-15-3</t>
+  </si>
+  <si>
+    <t>90-15-3
+1321-67-1</t>
+  </si>
+  <si>
+    <t>Acros</t>
+  </si>
+  <si>
+    <t>naphthalen-1-ol
+1-Naphthalenol
+alpha-naphthol
+1-Hydroxynaphthalene
+Furro ER</t>
+  </si>
+  <si>
+    <t>1-Hydroxynaphthalene</t>
+  </si>
+  <si>
+    <t>Keep in a dry, cool and well-ventilated place. Protect from direct sunlight. Incompatible Materials. Strong oxidizing agents. Strong bases. Halogens. Acid anhydrides. Acid chlorides.</t>
+  </si>
+  <si>
+    <t>C10H8O</t>
+  </si>
+  <si>
+    <t>H302: Harmful if swallowed [Warning Acute toxicity, oral]
+H312: Harmful in contact with skin [Warning Acute toxicity, dermal]
+H315: Causes skin irritation [Warning Skin corrosion/irritation]
+H318: Causes serious eye damage [Danger Serious eye damage/eye irritation]
+H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H311 (31.8%): Toxic in contact with skin [Danger Acute toxicity, dermal]
+H317 (25%): May cause an allergic skin reaction [Warning Sensitization, Skin]
+H400 (24.7%): Very toxic to aquatic life [Warning Hazardous to the aquatic environment, acute hazard]
+H410 (18%): Very toxic to aquatic life with long lasting effects [Warning Hazardous to the aquatic environment, long-term hazard]
+H412 (23.6%): Harmful to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]
+H314: Causes severe skin burns and eye damage [Danger Skin corrosion/irritation]
+H371: May cause damage to organs [Warning Specific target organ toxicity, single exposure]
+H411: Toxic to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]</t>
+  </si>
+  <si>
+    <t>CO
+IR
+AC
+EN
+CA</t>
+  </si>
+  <si>
+    <t>144.17</t>
+  </si>
+  <si>
+    <t>B- 5</t>
+  </si>
+  <si>
+    <t>acetone</t>
+  </si>
+  <si>
+    <t>Acetone</t>
+  </si>
+  <si>
+    <t>Causes serious eye irritation 
+May cause drowsiness or dizziness  Serious Eye Damage/Eye Irritation 
+May cause damage to organs through prolonged or repeated exposure</t>
+  </si>
+  <si>
+    <t>Flammable
+Irritant
+Health Hazard</t>
+  </si>
+  <si>
+    <t>Solvent</t>
+  </si>
+  <si>
+    <t>67-64-1</t>
+  </si>
+  <si>
+    <t>Brand Nu</t>
+  </si>
+  <si>
+    <t>2-propanone
+propanone
+Dimethyl ketone
+propan-2-one
+Methyl ketone</t>
+  </si>
+  <si>
+    <t>2-Propanone</t>
+  </si>
+  <si>
+    <t>Flammables area. Keep containers tightly closed in a dry, cool and well-ventilated place. Keep away from heat, sparks and flame. Incompatible Materials. Strong oxidizing agents. Strong reducing agents. Strong bases. Peroxides. Halogenated compounds. Alkali metals. Amines.</t>
+  </si>
+  <si>
+    <t>C3H6O</t>
+  </si>
+  <si>
+    <t>H225: Highly Flammable liquid and vapor [Danger Flammable liquids]
+H319: Causes serious eye irritation [Warning Serious eye damage/eye irritation]
+H336: May cause drowsiness or dizziness [Warning Specific target organ toxicity, single exposure; Narcotic effects]
+H305: May be harmful if swallowed and enters airways [Warning Aspiration hazard]
+H320: Causes eye irritation [Warning Serious eye damage/eye irritation]
+H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H361: Suspected of damaging fertility or the unborn child [Warning Reproductive toxicity]
+H373: May causes damage to organs through prolonged or repeated exposure [Warning Specific target organ toxicity, repeated exposure]
+H372: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]</t>
+  </si>
+  <si>
+    <t>FL
+IR
+CA</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>58.08</t>
+  </si>
+  <si>
+    <t>6-147</t>
+  </si>
+  <si>
+    <t>Flamm. Cab. (S3)</t>
+  </si>
   <si>
     <r>
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Summary and Success Report
 </t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Total Chemicals ran:
 </t>
     </r>
@@ -31,21 +390,39 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
-      <t>1</t>
+      <t>3</t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 _______________________________
 </t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Successful SDS Sheets</t>
     </r>
     <r>
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
 Total: </t>
@@ -54,13 +431,17 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
-      <t>1</t>
+      <t>3</t>
     </r>
     <r>
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
 Percentage: </t>
@@ -69,6 +450,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>100</t>
     </r>
@@ -76,21 +459,39 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>%</t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 _______________________________
 </t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>SDS Sheets that need review</t>
     </r>
     <r>
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
 Total: </t>
@@ -99,6 +500,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>0</t>
     </r>
@@ -106,6 +509,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
 Percentage: </t>
@@ -114,6 +519,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>0</t>
     </r>
@@ -121,21 +528,39 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>%</t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 _______________________________
 </t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Failed SDS Sheets</t>
     </r>
     <r>
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
 Total: </t>
@@ -144,6 +569,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>0</t>
     </r>
@@ -151,6 +578,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
 Percentage: </t>
@@ -159,6 +588,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>0</t>
     </r>
@@ -166,21 +597,39 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>%</t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 _______________________________
 </t>
     </r>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Errors encountered</t>
     </r>
     <r>
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
 Total: </t>
@@ -189,6 +638,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>0</t>
     </r>
@@ -196,6 +647,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
 Percentage: </t>
@@ -204,6 +657,8 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>0</t>
     </r>
@@ -211,115 +666,51 @@
       <rPr>
         <b/>
         <u/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
       </rPr>
       <t>%</t>
     </r>
-  </si>
-  <si>
-    <t>Search</t>
-  </si>
-  <si>
-    <t>Barium nitrate</t>
-  </si>
-  <si>
-    <t>✅✅ Extremely Confident</t>
-  </si>
-  <si>
-    <t>10022-31-8</t>
-  </si>
-  <si>
-    <t>BARIUM NITRATE</t>
-  </si>
-  <si>
-    <t>Pictograms</t>
-  </si>
-  <si>
-    <t>Inorganic salt</t>
-  </si>
-  <si>
-    <t>No date</t>
-  </si>
-  <si>
-    <t>Barium dinitrate; Nitric acid, barium salt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molecular Formulas (normalized) do not match
-SDS: BAN2O6
-PubChem: BA(NO3)2
-Penalty: -10</t>
-  </si>
-  <si>
-    <t>BaN2O6</t>
-  </si>
-  <si>
-    <t>Ba(NO3)2</t>
-  </si>
-  <si>
-    <t>261.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oxidizer
-Acute Toxic
-Irritant
-Health Hazard</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>EM Science</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t>6-144</t>
-  </si>
-  <si>
-    <t>A-1</t>
-  </si>
-  <si>
-    <t>Keep containers tightly closed in a dry, cool and well-ventilated place. Do not store near combustible materials. Incompatible Materials. Organic materials. Acids. Bases. Acid anhydrides. Metals. Reducing Agent. Strong reducing agents. Combustible material.</t>
-  </si>
-  <si>
-    <t>https://www.fishersci.com/store/msds?partNumber=AC192555000&amp;productDescription=barium-nitrate-acs-reag-kg&amp;vendorId=VN00032119&amp;keyword=true&amp;countryCode=US&amp;language=en</t>
-  </si>
-  <si>
-    <t>24-Dec-2021</t>
-  </si>
-  <si>
-    <t>importedProductName</t>
-  </si>
-  <si>
-    <t>sdsConfidenceScore</t>
-  </si>
-  <si>
-    <t>classification</t>
-  </si>
-  <si>
-    <t>sdsRevisionDate</t>
-  </si>
-  <si>
-    <t>searchQuery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFDDDDDD"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFDDDDDD"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -328,7 +719,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="28e482"/>
+        <fgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28E482"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF686B69"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFD1D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -341,17 +747,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <bottom style="medium">
+        <color rgb="FFDDDDDD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -359,19 +765,70 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,272 +1168,1978 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="100" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" customWidth="1"/>
+    <col min="3" max="3" width="60" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16" style="3" customWidth="1"/>
+    <col min="6" max="6" width="60" style="3" customWidth="1"/>
+    <col min="7" max="7" width="44" style="3" customWidth="1"/>
+    <col min="8" max="9" width="60" style="4" customWidth="1"/>
+    <col min="10" max="10" width="11" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16" style="2" customWidth="1"/>
+    <col min="13" max="13" width="60" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="1:13" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17"/>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="17"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="8">
+        <v>90</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="8">
+        <v>500</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="20"/>
+      <c r="M5" s="21"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="21"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="20"/>
+      <c r="M7" s="21"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="13"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="15">
+        <v>41435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="8">
+        <v>100</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="8">
+        <v>50</v>
+      </c>
+      <c r="L11" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L12" s="20"/>
+      <c r="M12" s="21"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L13" s="20"/>
+      <c r="M13" s="21"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="20"/>
+      <c r="M14" s="21"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="15">
+        <v>42376</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="8">
+        <v>100</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="8">
+        <v>12.6</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L19" s="20"/>
+      <c r="M19" s="21"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="18"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L20" s="20"/>
+      <c r="M20" s="21"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="18"/>
+      <c r="B21" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="20"/>
+      <c r="M21" s="21"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="11"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="L18:L21"/>
+    <mergeCell ref="M18:M21"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="L11:L14"/>
+    <mergeCell ref="M11:M14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="H9:H11"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="L4:L7"/>
+    <mergeCell ref="M4:M7"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="M3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M17" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="3" width="89" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="1" customWidth="1"/>
-    <col min="8" max="8" width="45" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="1" customWidth="1"/>
-    <col min="10" max="10" width="2" style="1" customWidth="1"/>
-    <col min="11" max="11" width="45" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5" style="1" customWidth="1"/>
-    <col min="15" max="16" width="100" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="4">
-        <v>90</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="3"/>
-      <c r="M1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="4">
-        <v>500</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>22</v>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A1:A6"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="5" width="17" style="1" customWidth="1"/>
+    <col min="1" max="13" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <f>='Full Data'!B1</f>
-      </c>
-      <c r="B2" s="2">
-        <f>='Full Data'!C1</f>
-      </c>
-      <c r="C2" s="2">
-        <f>='Full Data'!M1</f>
-      </c>
-      <c r="D2" s="2">
-        <f>='Full Data'!Q6</f>
-      </c>
-      <c r="E2" s="2">
-        <f>='Full Data'!E1</f>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>'Full Data'!A2</f>
+        <v>Barium nitrate</v>
+      </c>
+      <c r="B2" t="str">
+        <f>'Full Data'!B2</f>
+        <v>STATUS CODE:</v>
+      </c>
+      <c r="C2" t="str">
+        <f>'Full Data'!C2</f>
+        <v>✅✅ Extremely Confident</v>
+      </c>
+      <c r="D2" t="str">
+        <f>'Full Data'!D2</f>
+        <v xml:space="preserve">NAME: </v>
+      </c>
+      <c r="E2" t="str">
+        <f>'Full Data'!E2</f>
+        <v>Barium nitrate</v>
+      </c>
+      <c r="F2" t="str">
+        <f>'Full Data'!F2</f>
+        <v>BARIUM NITRATE</v>
+      </c>
+      <c r="G2" t="str">
+        <f>'Full Data'!G2</f>
+        <v>Barium nitrate</v>
+      </c>
+      <c r="H2" t="str">
+        <f>'Full Data'!H2</f>
+        <v xml:space="preserve">May intensify fire; oxidizer 
+Toxic if swallowed 
+Causes serious eye irritation </v>
+      </c>
+      <c r="I2" t="str">
+        <f>'Full Data'!I2</f>
+        <v>Oxidizer
+Acute Toxic
+Irritant
+Health Hazard</v>
+      </c>
+      <c r="J2" t="str">
+        <f>'Full Data'!J2</f>
+        <v>CLASS:</v>
+      </c>
+      <c r="K2" t="str">
+        <f>'Full Data'!K2</f>
+        <v>Inorganic salt</v>
+      </c>
+      <c r="L2" t="str">
+        <f>'Full Data'!L2</f>
+        <v>RECEIVED DATE</v>
+      </c>
+      <c r="M2" t="str">
+        <f>'Full Data'!M2</f>
+        <v>No date</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <f>'Full Data'!A3</f>
+        <v>0</v>
+      </c>
+      <c r="B3" t="str">
+        <f>'Full Data'!B3</f>
+        <v>CONFIDENCE SCORE:</v>
+      </c>
+      <c r="C3">
+        <f>'Full Data'!C3</f>
+        <v>90</v>
+      </c>
+      <c r="D3" t="str">
+        <f>'Full Data'!D3</f>
+        <v>CAS NO.:</v>
+      </c>
+      <c r="E3" t="str">
+        <f>'Full Data'!E3</f>
+        <v>10022-31-8</v>
+      </c>
+      <c r="F3" t="str">
+        <f>'Full Data'!F3</f>
+        <v>10022-31-8</v>
+      </c>
+      <c r="G3" t="str">
+        <f>'Full Data'!G3</f>
+        <v>10022-31-8</v>
+      </c>
+      <c r="H3">
+        <f>'Full Data'!H3</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>'Full Data'!I3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" t="str">
+        <f>'Full Data'!J3</f>
+        <v>SUPPLIER:</v>
+      </c>
+      <c r="K3" t="str">
+        <f>'Full Data'!K3</f>
+        <v>EM Science</v>
+      </c>
+      <c r="L3" t="str">
+        <f>'Full Data'!L3</f>
+        <v xml:space="preserve">SDS LINK: </v>
+      </c>
+      <c r="M3" t="str">
+        <f>'Full Data'!M3</f>
+        <v>Click for SDS.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <f>'Full Data'!A4</f>
+        <v>0</v>
+      </c>
+      <c r="B4" t="str">
+        <f>'Full Data'!B4</f>
+        <v>CONF. SCORE INFO:</v>
+      </c>
+      <c r="C4" t="str">
+        <f>'Full Data'!C4</f>
+        <v>Molecular Formulas (normalized) do not match
+SDS: BAN2O6
+PubChem: BA(NO3)2
+Penalty: -10</v>
+      </c>
+      <c r="D4" t="str">
+        <f>'Full Data'!D4</f>
+        <v>SYNONYMS:</v>
+      </c>
+      <c r="E4" t="str">
+        <f>'Full Data'!E4</f>
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <f>'Full Data'!F4</f>
+        <v>Nitrobarite
+Nitric acid, barium salt
+Barium dinitrate
+Nitrate de baryum
+Nitrato barico</v>
+      </c>
+      <c r="G4" t="str">
+        <f>'Full Data'!G4</f>
+        <v>Barium dinitrate; Nitric acid
+barium salt.</v>
+      </c>
+      <c r="H4">
+        <f>'Full Data'!H4</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f>'Full Data'!I4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" t="str">
+        <f>'Full Data'!J4</f>
+        <v>QUANTITY:</v>
+      </c>
+      <c r="K4">
+        <f>'Full Data'!K4</f>
+        <v>500</v>
+      </c>
+      <c r="L4" t="str">
+        <f>'Full Data'!L4</f>
+        <v>STORAGE NOTES:</v>
+      </c>
+      <c r="M4" t="str">
+        <f>'Full Data'!M4</f>
+        <v>Keep containers tightly closed in a dry, cool and well-ventilated place. Do not store near combustible materials. Incompatible Materials. Organic materials. Acids. Bases. Acid anhydrides. Metals. Reducing Agent. Strong reducing agents. Combustible material.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f>'Full Data'!A5</f>
+        <v>10022-31-8</v>
+      </c>
+      <c r="B5">
+        <f>'Full Data'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f>'Full Data'!C5</f>
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <f>'Full Data'!D5</f>
+        <v>FORMULA:</v>
+      </c>
+      <c r="E5" t="str">
+        <f>'Full Data'!E5</f>
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <f>'Full Data'!F5</f>
+        <v>Ba(NO3)2</v>
+      </c>
+      <c r="G5" t="str">
+        <f>'Full Data'!G5</f>
+        <v>BaN2O6</v>
+      </c>
+      <c r="H5" t="str">
+        <f>'Full Data'!H5</f>
+        <v>H272 (68.7%): May intensify fire; oxidizer [Danger Oxidizing liquids; Oxidizing solids]
+H301 (12.2%): Toxic if swallowed [Danger Acute toxicity, oral]
+H302 (86.6%): Harmful if swallowed [Warning Acute toxicity, oral]
+H319 (24.8%): Causes serious eye irritation [Warning Serious eye damage/eye irritation]
+H332 (98.8%): Harmful if inhaled [Warning Acute toxicity, inhalation]
+H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H336: May cause drowsiness or dizziness [Warning Specific target organ toxicity, single exposure; Narcotic effects]
+H370: Causes damage to organs [Danger Specific target organ toxicity, single exposure]
+H371: May cause damage to organs [Warning Specific target organ toxicity, single exposure]
+H372: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]
+H316: Causes mild skin irritation [Warning Skin corrosion/irritation]</v>
+      </c>
+      <c r="I5" t="str">
+        <f>'Full Data'!I5</f>
+        <v>OX
+AC
+IR
+CA</v>
+      </c>
+      <c r="J5" t="str">
+        <f>'Full Data'!J5</f>
+        <v>UNITS:</v>
+      </c>
+      <c r="K5" t="str">
+        <f>'Full Data'!K5</f>
+        <v>g</v>
+      </c>
+      <c r="L5">
+        <f>'Full Data'!L5</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f>'Full Data'!M5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f>'Full Data'!A6</f>
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <f>'Full Data'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f>'Full Data'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" t="str">
+        <f>'Full Data'!D6</f>
+        <v>MW:</v>
+      </c>
+      <c r="E6" t="str">
+        <f>'Full Data'!E6</f>
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <f>'Full Data'!F6</f>
+        <v>261.34</v>
+      </c>
+      <c r="G6" t="str">
+        <f>'Full Data'!G6</f>
+        <v>261.34</v>
+      </c>
+      <c r="H6">
+        <f>'Full Data'!H6</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>'Full Data'!I6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" t="str">
+        <f>'Full Data'!J6</f>
+        <v>LOCATION:</v>
+      </c>
+      <c r="K6" t="str">
+        <f>'Full Data'!K6</f>
+        <v>6-144</v>
+      </c>
+      <c r="L6">
+        <f>'Full Data'!L6</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>'Full Data'!M6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <f>'Full Data'!A7</f>
+        <v>0</v>
+      </c>
+      <c r="B7" t="str">
+        <f>'Full Data'!B7</f>
+        <v>ERRORS:</v>
+      </c>
+      <c r="C7" t="str">
+        <f>'Full Data'!C7</f>
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <f>'Full Data'!D7</f>
+        <v>SIGNAL WORD:</v>
+      </c>
+      <c r="E7" t="str">
+        <f>'Full Data'!E7</f>
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <f>'Full Data'!F7</f>
+        <v>Danger</v>
+      </c>
+      <c r="G7" t="str">
+        <f>'Full Data'!G7</f>
+        <v>Danger</v>
+      </c>
+      <c r="H7">
+        <f>'Full Data'!H7</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f>'Full Data'!I7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" t="str">
+        <f>'Full Data'!J7</f>
+        <v>CABINET:</v>
+      </c>
+      <c r="K7" t="str">
+        <f>'Full Data'!K7</f>
+        <v>A-1</v>
+      </c>
+      <c r="L7">
+        <f>'Full Data'!L7</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f>'Full Data'!M7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f>'Full Data'!A8</f>
+        <v>0</v>
+      </c>
+      <c r="B8">
+        <f>'Full Data'!B8</f>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f>'Full Data'!C8</f>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f>'Full Data'!D8</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>'Full Data'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f>'Full Data'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f>'Full Data'!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f>'Full Data'!H8</f>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f>'Full Data'!I8</f>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f>'Full Data'!J8</f>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f>'Full Data'!K8</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>'Full Data'!L8</f>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f>'Full Data'!M8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f>'Full Data'!A9</f>
+        <v>1-napthol</v>
+      </c>
+      <c r="B9" t="str">
+        <f>'Full Data'!B9</f>
+        <v>STATUS CODE:</v>
+      </c>
+      <c r="C9" t="str">
+        <f>'Full Data'!C9</f>
+        <v>✅✅ Extremely Confident</v>
+      </c>
+      <c r="D9" t="str">
+        <f>'Full Data'!D9</f>
+        <v xml:space="preserve">NAME: </v>
+      </c>
+      <c r="E9" t="str">
+        <f>'Full Data'!E9</f>
+        <v>1-napthol</v>
+      </c>
+      <c r="F9" t="str">
+        <f>'Full Data'!F9</f>
+        <v>1-NAPHTHOL</v>
+      </c>
+      <c r="G9" t="str">
+        <f>'Full Data'!G9</f>
+        <v>1-Naphthol</v>
+      </c>
+      <c r="H9" t="str">
+        <f>'Full Data'!H9</f>
+        <v>Causes skin irritation 
+Causes serious eye damage 
+May cause respiratory irritation 
+Harmful if swallowed or in contact with skin</v>
+      </c>
+      <c r="I9" t="str">
+        <f>'Full Data'!I9</f>
+        <v>Corrosive
+Irritant
+Acute Toxic
+Environmental Hazard
+Health Hazard</v>
+      </c>
+      <c r="J9" t="str">
+        <f>'Full Data'!J9</f>
+        <v>CLASS:</v>
+      </c>
+      <c r="K9" t="str">
+        <f>'Full Data'!K9</f>
+        <v>Organic compound</v>
+      </c>
+      <c r="L9" t="str">
+        <f>'Full Data'!L9</f>
+        <v>RECEIVED DATE</v>
+      </c>
+      <c r="M9">
+        <f>'Full Data'!M9</f>
+        <v>41435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f>'Full Data'!A10</f>
+        <v>0</v>
+      </c>
+      <c r="B10" t="str">
+        <f>'Full Data'!B10</f>
+        <v>CONFIDENCE SCORE:</v>
+      </c>
+      <c r="C10">
+        <f>'Full Data'!C10</f>
+        <v>100</v>
+      </c>
+      <c r="D10" t="str">
+        <f>'Full Data'!D10</f>
+        <v>CAS NO.:</v>
+      </c>
+      <c r="E10" t="str">
+        <f>'Full Data'!E10</f>
+        <v>90-15-3</v>
+      </c>
+      <c r="F10" t="str">
+        <f>'Full Data'!F10</f>
+        <v>90-15-3
+1321-67-1</v>
+      </c>
+      <c r="G10" t="str">
+        <f>'Full Data'!G10</f>
+        <v>90-15-3</v>
+      </c>
+      <c r="H10">
+        <f>'Full Data'!H10</f>
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f>'Full Data'!I10</f>
+        <v>0</v>
+      </c>
+      <c r="J10" t="str">
+        <f>'Full Data'!J10</f>
+        <v>SUPPLIER:</v>
+      </c>
+      <c r="K10" t="str">
+        <f>'Full Data'!K10</f>
+        <v>Acros</v>
+      </c>
+      <c r="L10" t="str">
+        <f>'Full Data'!L10</f>
+        <v xml:space="preserve">SDS LINK: </v>
+      </c>
+      <c r="M10" t="str">
+        <f>'Full Data'!M10</f>
+        <v>Click for SDS.</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f>'Full Data'!A11</f>
+        <v>0</v>
+      </c>
+      <c r="B11" t="str">
+        <f>'Full Data'!B11</f>
+        <v>CONF. SCORE INFO:</v>
+      </c>
+      <c r="C11" t="str">
+        <f>'Full Data'!C11</f>
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <f>'Full Data'!D11</f>
+        <v>SYNONYMS:</v>
+      </c>
+      <c r="E11" t="str">
+        <f>'Full Data'!E11</f>
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <f>'Full Data'!F11</f>
+        <v>naphthalen-1-ol
+1-Naphthalenol
+alpha-naphthol
+1-Hydroxynaphthalene
+Furro ER</v>
+      </c>
+      <c r="G11" t="str">
+        <f>'Full Data'!G11</f>
+        <v>1-Hydroxynaphthalene</v>
+      </c>
+      <c r="H11">
+        <f>'Full Data'!H11</f>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f>'Full Data'!I11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" t="str">
+        <f>'Full Data'!J11</f>
+        <v>QUANTITY:</v>
+      </c>
+      <c r="K11">
+        <f>'Full Data'!K11</f>
+        <v>50</v>
+      </c>
+      <c r="L11" t="str">
+        <f>'Full Data'!L11</f>
+        <v>STORAGE NOTES:</v>
+      </c>
+      <c r="M11" t="str">
+        <f>'Full Data'!M11</f>
+        <v>Keep in a dry, cool and well-ventilated place. Protect from direct sunlight. Incompatible Materials. Strong oxidizing agents. Strong bases. Halogens. Acid anhydrides. Acid chlorides.</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
+        <f>'Full Data'!A12</f>
+        <v>90-15-3</v>
+      </c>
+      <c r="B12">
+        <f>'Full Data'!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f>'Full Data'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D12" t="str">
+        <f>'Full Data'!D12</f>
+        <v>FORMULA:</v>
+      </c>
+      <c r="E12" t="str">
+        <f>'Full Data'!E12</f>
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <f>'Full Data'!F12</f>
+        <v>C10H8O</v>
+      </c>
+      <c r="G12" t="str">
+        <f>'Full Data'!G12</f>
+        <v>C10H8O</v>
+      </c>
+      <c r="H12" t="str">
+        <f>'Full Data'!H12</f>
+        <v>H302: Harmful if swallowed [Warning Acute toxicity, oral]
+H312: Harmful in contact with skin [Warning Acute toxicity, dermal]
+H315: Causes skin irritation [Warning Skin corrosion/irritation]
+H318: Causes serious eye damage [Danger Serious eye damage/eye irritation]
+H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H311 (31.8%): Toxic in contact with skin [Danger Acute toxicity, dermal]
+H317 (25%): May cause an allergic skin reaction [Warning Sensitization, Skin]
+H400 (24.7%): Very toxic to aquatic life [Warning Hazardous to the aquatic environment, acute hazard]
+H410 (18%): Very toxic to aquatic life with long lasting effects [Warning Hazardous to the aquatic environment, long-term hazard]
+H412 (23.6%): Harmful to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]
+H314: Causes severe skin burns and eye damage [Danger Skin corrosion/irritation]
+H371: May cause damage to organs [Warning Specific target organ toxicity, single exposure]
+H411: Toxic to aquatic life with long lasting effects [Hazardous to the aquatic environment, long-term hazard]</v>
+      </c>
+      <c r="I12" t="str">
+        <f>'Full Data'!I12</f>
+        <v>CO
+IR
+AC
+EN
+CA</v>
+      </c>
+      <c r="J12" t="str">
+        <f>'Full Data'!J12</f>
+        <v>UNITS:</v>
+      </c>
+      <c r="K12" t="str">
+        <f>'Full Data'!K12</f>
+        <v>g</v>
+      </c>
+      <c r="L12">
+        <f>'Full Data'!L12</f>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f>'Full Data'!M12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f>'Full Data'!A13</f>
+        <v>0</v>
+      </c>
+      <c r="B13">
+        <f>'Full Data'!B13</f>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f>'Full Data'!C13</f>
+        <v>0</v>
+      </c>
+      <c r="D13" t="str">
+        <f>'Full Data'!D13</f>
+        <v>MW:</v>
+      </c>
+      <c r="E13" t="str">
+        <f>'Full Data'!E13</f>
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <f>'Full Data'!F13</f>
+        <v>144.17</v>
+      </c>
+      <c r="G13" t="str">
+        <f>'Full Data'!G13</f>
+        <v>144.17</v>
+      </c>
+      <c r="H13">
+        <f>'Full Data'!H13</f>
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f>'Full Data'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" t="str">
+        <f>'Full Data'!J13</f>
+        <v>LOCATION:</v>
+      </c>
+      <c r="K13" t="str">
+        <f>'Full Data'!K13</f>
+        <v>6-144</v>
+      </c>
+      <c r="L13">
+        <f>'Full Data'!L13</f>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f>'Full Data'!M13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f>'Full Data'!A14</f>
+        <v>0</v>
+      </c>
+      <c r="B14" t="str">
+        <f>'Full Data'!B14</f>
+        <v>ERRORS:</v>
+      </c>
+      <c r="C14" t="str">
+        <f>'Full Data'!C14</f>
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <f>'Full Data'!D14</f>
+        <v>SIGNAL WORD:</v>
+      </c>
+      <c r="E14" t="str">
+        <f>'Full Data'!E14</f>
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <f>'Full Data'!F14</f>
+        <v>Danger</v>
+      </c>
+      <c r="G14" t="str">
+        <f>'Full Data'!G14</f>
+        <v>Danger</v>
+      </c>
+      <c r="H14">
+        <f>'Full Data'!H14</f>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f>'Full Data'!I14</f>
+        <v>0</v>
+      </c>
+      <c r="J14" t="str">
+        <f>'Full Data'!J14</f>
+        <v>CABINET:</v>
+      </c>
+      <c r="K14" t="str">
+        <f>'Full Data'!K14</f>
+        <v>B- 5</v>
+      </c>
+      <c r="L14">
+        <f>'Full Data'!L14</f>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f>'Full Data'!M14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f>'Full Data'!A15</f>
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <f>'Full Data'!B15</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f>'Full Data'!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f>'Full Data'!D15</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>'Full Data'!E15</f>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>'Full Data'!F15</f>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f>'Full Data'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <f>'Full Data'!H15</f>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f>'Full Data'!I15</f>
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f>'Full Data'!J15</f>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f>'Full Data'!K15</f>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f>'Full Data'!L15</f>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f>'Full Data'!M15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <f>'Full Data'!A16</f>
+        <v>acetone</v>
+      </c>
+      <c r="B16" t="str">
+        <f>'Full Data'!B16</f>
+        <v>STATUS CODE:</v>
+      </c>
+      <c r="C16" t="str">
+        <f>'Full Data'!C16</f>
+        <v>✅✅ Extremely Confident</v>
+      </c>
+      <c r="D16" t="str">
+        <f>'Full Data'!D16</f>
+        <v xml:space="preserve">NAME: </v>
+      </c>
+      <c r="E16" t="str">
+        <f>'Full Data'!E16</f>
+        <v>acetone</v>
+      </c>
+      <c r="F16" t="str">
+        <f>'Full Data'!F16</f>
+        <v>acetone</v>
+      </c>
+      <c r="G16" t="str">
+        <f>'Full Data'!G16</f>
+        <v>Acetone</v>
+      </c>
+      <c r="H16" t="str">
+        <f>'Full Data'!H16</f>
+        <v>Causes serious eye irritation 
+May cause drowsiness or dizziness  Serious Eye Damage/Eye Irritation 
+May cause damage to organs through prolonged or repeated exposure</v>
+      </c>
+      <c r="I16" t="str">
+        <f>'Full Data'!I16</f>
+        <v>Flammable
+Irritant
+Health Hazard</v>
+      </c>
+      <c r="J16" t="str">
+        <f>'Full Data'!J16</f>
+        <v>CLASS:</v>
+      </c>
+      <c r="K16" t="str">
+        <f>'Full Data'!K16</f>
+        <v>Solvent</v>
+      </c>
+      <c r="L16" t="str">
+        <f>'Full Data'!L16</f>
+        <v>RECEIVED DATE</v>
+      </c>
+      <c r="M16">
+        <f>'Full Data'!M16</f>
+        <v>42376</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <f>'Full Data'!A17</f>
+        <v>0</v>
+      </c>
+      <c r="B17" t="str">
+        <f>'Full Data'!B17</f>
+        <v>CONFIDENCE SCORE:</v>
+      </c>
+      <c r="C17">
+        <f>'Full Data'!C17</f>
+        <v>100</v>
+      </c>
+      <c r="D17" t="str">
+        <f>'Full Data'!D17</f>
+        <v>CAS NO.:</v>
+      </c>
+      <c r="E17" t="str">
+        <f>'Full Data'!E17</f>
+        <v>67-64-1</v>
+      </c>
+      <c r="F17" t="str">
+        <f>'Full Data'!F17</f>
+        <v>67-64-1</v>
+      </c>
+      <c r="G17" t="str">
+        <f>'Full Data'!G17</f>
+        <v>67-64-1</v>
+      </c>
+      <c r="H17">
+        <f>'Full Data'!H17</f>
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <f>'Full Data'!I17</f>
+        <v>0</v>
+      </c>
+      <c r="J17" t="str">
+        <f>'Full Data'!J17</f>
+        <v>SUPPLIER:</v>
+      </c>
+      <c r="K17" t="str">
+        <f>'Full Data'!K17</f>
+        <v>Brand Nu</v>
+      </c>
+      <c r="L17" t="str">
+        <f>'Full Data'!L17</f>
+        <v xml:space="preserve">SDS LINK: </v>
+      </c>
+      <c r="M17" t="str">
+        <f>'Full Data'!M17</f>
+        <v>Click for SDS.</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <f>'Full Data'!A18</f>
+        <v>0</v>
+      </c>
+      <c r="B18" t="str">
+        <f>'Full Data'!B18</f>
+        <v>CONF. SCORE INFO:</v>
+      </c>
+      <c r="C18" t="str">
+        <f>'Full Data'!C18</f>
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <f>'Full Data'!D18</f>
+        <v>SYNONYMS:</v>
+      </c>
+      <c r="E18" t="str">
+        <f>'Full Data'!E18</f>
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <f>'Full Data'!F18</f>
+        <v>2-propanone
+propanone
+Dimethyl ketone
+propan-2-one
+Methyl ketone</v>
+      </c>
+      <c r="G18" t="str">
+        <f>'Full Data'!G18</f>
+        <v>2-Propanone</v>
+      </c>
+      <c r="H18">
+        <f>'Full Data'!H18</f>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f>'Full Data'!I18</f>
+        <v>0</v>
+      </c>
+      <c r="J18" t="str">
+        <f>'Full Data'!J18</f>
+        <v>QUANTITY:</v>
+      </c>
+      <c r="K18">
+        <f>'Full Data'!K18</f>
+        <v>12.6</v>
+      </c>
+      <c r="L18" t="str">
+        <f>'Full Data'!L18</f>
+        <v>STORAGE NOTES:</v>
+      </c>
+      <c r="M18" t="str">
+        <f>'Full Data'!M18</f>
+        <v>Flammables area. Keep containers tightly closed in a dry, cool and well-ventilated place. Keep away from heat, sparks and flame. Incompatible Materials. Strong oxidizing agents. Strong reducing agents. Strong bases. Peroxides. Halogenated compounds. Alkali metals. Amines.</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" t="str">
+        <f>'Full Data'!A19</f>
+        <v>67-64-1</v>
+      </c>
+      <c r="B19">
+        <f>'Full Data'!B19</f>
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <f>'Full Data'!C19</f>
+        <v>0</v>
+      </c>
+      <c r="D19" t="str">
+        <f>'Full Data'!D19</f>
+        <v>FORMULA:</v>
+      </c>
+      <c r="E19" t="str">
+        <f>'Full Data'!E19</f>
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <f>'Full Data'!F19</f>
+        <v>C3H6O</v>
+      </c>
+      <c r="G19" t="str">
+        <f>'Full Data'!G19</f>
+        <v>C3H6O</v>
+      </c>
+      <c r="H19" t="str">
+        <f>'Full Data'!H19</f>
+        <v>H225: Highly Flammable liquid and vapor [Danger Flammable liquids]
+H319: Causes serious eye irritation [Warning Serious eye damage/eye irritation]
+H336: May cause drowsiness or dizziness [Warning Specific target organ toxicity, single exposure; Narcotic effects]
+H305: May be harmful if swallowed and enters airways [Warning Aspiration hazard]
+H320: Causes eye irritation [Warning Serious eye damage/eye irritation]
+H335: May cause respiratory irritation [Warning Specific target organ toxicity, single exposure; Respiratory tract irritation]
+H361: Suspected of damaging fertility or the unborn child [Warning Reproductive toxicity]
+H373: May causes damage to organs through prolonged or repeated exposure [Warning Specific target organ toxicity, repeated exposure]
+H372: Causes damage to organs through prolonged or repeated exposure [Danger Specific target organ toxicity, repeated exposure]</v>
+      </c>
+      <c r="I19" t="str">
+        <f>'Full Data'!I19</f>
+        <v>FL
+IR
+CA</v>
+      </c>
+      <c r="J19" t="str">
+        <f>'Full Data'!J19</f>
+        <v>UNITS:</v>
+      </c>
+      <c r="K19" t="str">
+        <f>'Full Data'!K19</f>
+        <v>L</v>
+      </c>
+      <c r="L19">
+        <f>'Full Data'!L19</f>
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <f>'Full Data'!M19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <f>'Full Data'!A20</f>
+        <v>0</v>
+      </c>
+      <c r="B20">
+        <f>'Full Data'!B20</f>
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <f>'Full Data'!C20</f>
+        <v>0</v>
+      </c>
+      <c r="D20" t="str">
+        <f>'Full Data'!D20</f>
+        <v>MW:</v>
+      </c>
+      <c r="E20" t="str">
+        <f>'Full Data'!E20</f>
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <f>'Full Data'!F20</f>
+        <v>58.08</v>
+      </c>
+      <c r="G20" t="str">
+        <f>'Full Data'!G20</f>
+        <v>58.08</v>
+      </c>
+      <c r="H20">
+        <f>'Full Data'!H20</f>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <f>'Full Data'!I20</f>
+        <v>0</v>
+      </c>
+      <c r="J20" t="str">
+        <f>'Full Data'!J20</f>
+        <v>LOCATION:</v>
+      </c>
+      <c r="K20" t="str">
+        <f>'Full Data'!K20</f>
+        <v>6-147</v>
+      </c>
+      <c r="L20">
+        <f>'Full Data'!L20</f>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f>'Full Data'!M20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <f>'Full Data'!A21</f>
+        <v>0</v>
+      </c>
+      <c r="B21" t="str">
+        <f>'Full Data'!B21</f>
+        <v>ERRORS:</v>
+      </c>
+      <c r="C21" t="str">
+        <f>'Full Data'!C21</f>
+        <v/>
+      </c>
+      <c r="D21" t="str">
+        <f>'Full Data'!D21</f>
+        <v>SIGNAL WORD:</v>
+      </c>
+      <c r="E21" t="str">
+        <f>'Full Data'!E21</f>
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <f>'Full Data'!F21</f>
+        <v>Danger</v>
+      </c>
+      <c r="G21" t="str">
+        <f>'Full Data'!G21</f>
+        <v>Danger</v>
+      </c>
+      <c r="H21">
+        <f>'Full Data'!H21</f>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <f>'Full Data'!I21</f>
+        <v>0</v>
+      </c>
+      <c r="J21" t="str">
+        <f>'Full Data'!J21</f>
+        <v>CABINET:</v>
+      </c>
+      <c r="K21" t="str">
+        <f>'Full Data'!K21</f>
+        <v>Flamm. Cab. (S3)</v>
+      </c>
+      <c r="L21">
+        <f>'Full Data'!L21</f>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f>'Full Data'!M21</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>